--- a/data/projects/56A0TXN/早期介入/交付预案/输出结果/软件配置信息表.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/输出结果/软件配置信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,29 +466,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>操作系统</t>
+          <t>昇腾训练版本</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EulerOS</t>
+          <t>Ascend Training Solution</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>24.0.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>人工录入</t>
+          <t>自动解析</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -501,37 +501,251 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>操作系统</t>
+          <t>昇腾推理版本</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EulerOS</t>
+          <t>Ascend Inference Solution</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>24.0.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>操作系统</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FresBSD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>人工录入</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>待客户确认</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ASCEND HDK</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ASCEND HDK</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>存储 DPC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>存储 DPC</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CCAE AGENT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>iMaster CCAE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>V100R025C20SPC010</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>已生成风险 R-002</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CANN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CANN</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CANN 8.0.1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>操作系统</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EulerOS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
         </is>
